--- a/studio-di-fattibilita/allegati/energy-balance/energy_balance_summary.xlsx
+++ b/studio-di-fattibilita/allegati/energy-balance/energy_balance_summary.xlsx
@@ -232,7 +232,7 @@
       <row>105</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="14668500" cy="8001000"/>
+    <ext cx="18669000" cy="6667500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
